--- a/data/trans_bre/P3A_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 1,36</t>
+          <t>-11,4; 1,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -13,71</t>
+          <t>-27,09; -14,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,06; -10,34</t>
+          <t>-25,54; -10,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,88</t>
+          <t>-5,13; 8,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 8,11</t>
+          <t>-48,81; 11,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,31; -54,98</t>
+          <t>-80,42; -54,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,57; -37,36</t>
+          <t>-69,68; -38,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 36,54</t>
+          <t>-17,32; 43,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -5,5</t>
+          <t>-16,27; -6,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -5,76</t>
+          <t>-16,18; -6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -8,22</t>
+          <t>-18,76; -8,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -3,54</t>
+          <t>-15,76; -3,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,61; -24,52</t>
+          <t>-57,35; -27,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,77; -27,87</t>
+          <t>-60,94; -28,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -29,68</t>
+          <t>-58,32; -31,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,02; -9,76</t>
+          <t>-35,53; -8,98</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -5,92</t>
+          <t>-16,0; -5,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -9,6</t>
+          <t>-21,05; -8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,05; -10,67</t>
+          <t>-25,99; -11,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,23</t>
+          <t>-11,84; 1,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,72; -38,17</t>
+          <t>-73,02; -34,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,56; -42,0</t>
+          <t>-73,0; -39,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,53; -28,51</t>
+          <t>-57,18; -29,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 7,57</t>
+          <t>-31,25; 4,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 3,21</t>
+          <t>-7,84; 3,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -10,51</t>
+          <t>-22,89; -11,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,24; -12,63</t>
+          <t>-24,58; -12,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -10,82</t>
+          <t>-27,21; -10,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 18,71</t>
+          <t>-32,53; 20,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -40,31</t>
+          <t>-69,37; -42,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,27; -44,48</t>
+          <t>-70,32; -43,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,66; -39,22</t>
+          <t>-73,71; -36,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -3,21</t>
+          <t>-16,88; -3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 2,93</t>
+          <t>-11,67; 2,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -9,38</t>
+          <t>-25,99; -9,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 2,05</t>
+          <t>-14,97; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,77; -15,93</t>
+          <t>-68,16; -15,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 19,71</t>
+          <t>-49,65; 21,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -29,55</t>
+          <t>-63,85; -28,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 9,05</t>
+          <t>-57,85; 10,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 1,52</t>
+          <t>-10,89; 0,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -3,68</t>
+          <t>-18,42; -3,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -6,76</t>
+          <t>-20,8; -7,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 4,21</t>
+          <t>-10,51; 3,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 10,64</t>
+          <t>-52,09; 7,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,76; -14,5</t>
+          <t>-54,91; -13,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,4; -31,78</t>
+          <t>-70,89; -33,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 11,77</t>
+          <t>-23,28; 11,16</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,49; -8,9</t>
+          <t>-17,34; -8,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -5,13</t>
+          <t>-14,75; -5,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -0,62</t>
+          <t>-10,83; -1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,11; -2,55</t>
+          <t>-21,78; -2,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -42,55</t>
+          <t>-65,43; -39,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,39; -20,19</t>
+          <t>-48,7; -20,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,1; -2,38</t>
+          <t>-34,45; -4,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,36; -9,82</t>
+          <t>-69,0; -9,86</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -5,66</t>
+          <t>-12,44; -5,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -8,7</t>
+          <t>-17,02; -8,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -9,68</t>
+          <t>-18,75; -10,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -0,28</t>
+          <t>-12,84; -0,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,46; -33,17</t>
+          <t>-60,62; -32,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,81; -30,41</t>
+          <t>-53,04; -30,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,77; -29,28</t>
+          <t>-48,98; -29,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,45; -9,17</t>
+          <t>-73,64; -9,83</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -7,06</t>
+          <t>-10,78; -7,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -10,56</t>
+          <t>-14,62; -10,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -11,73</t>
+          <t>-16,0; -11,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,5</t>
+          <t>-10,67; -1,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,24; -35,97</t>
+          <t>-48,63; -35,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -39,8</t>
+          <t>-50,98; -40,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -37,36</t>
+          <t>-47,6; -37,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -9,71</t>
+          <t>-37,77; -7,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R1-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>-0,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 1,65</t>
+          <t>-12,3; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,09; -14,38</t>
+          <t>-27,23; -14,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,54; -10,79</t>
+          <t>-24,62; -10,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 8,93</t>
+          <t>-6,14; 6,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 11,31</t>
+          <t>-51,97; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,42; -54,62</t>
+          <t>-80,98; -53,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-69,68; -38,53</t>
+          <t>-69,49; -37,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 43,07</t>
+          <t>-21,56; 30,36</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-9,78</t>
+          <t>-10,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-24,27%</t>
+          <t>-25,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -6,16</t>
+          <t>-16,41; -6,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,18; -6,16</t>
+          <t>-16,33; -6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -8,09</t>
+          <t>-19,05; -8,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -3,25</t>
+          <t>-16,87; -4,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -27,47</t>
+          <t>-58,38; -27,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,94; -28,52</t>
+          <t>-61,34; -27,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,32; -31,12</t>
+          <t>-59,6; -32,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,53; -8,98</t>
+          <t>-37,21; -11,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,53</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,74%</t>
+          <t>-9,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -5,81</t>
+          <t>-16,59; -6,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -8,93</t>
+          <t>-21,05; -8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -11,33</t>
+          <t>-24,74; -10,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 1,27</t>
+          <t>-9,7; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,02; -34,67</t>
+          <t>-74,49; -36,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,0; -39,12</t>
+          <t>-72,48; -38,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,18; -29,7</t>
+          <t>-57,55; -29,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 4,21</t>
+          <t>-26,77; 10,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,85</t>
+          <t>-13,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-55,1%</t>
+          <t>-41,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,69</t>
+          <t>-7,56; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -11,05</t>
+          <t>-23,24; -10,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -12,32</t>
+          <t>-24,62; -11,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,21; -10,16</t>
+          <t>-20,36; -6,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 20,88</t>
+          <t>-32,01; 26,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,37; -42,18</t>
+          <t>-70,17; -41,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -43,54</t>
+          <t>-69,17; -41,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,71; -36,68</t>
+          <t>-56,45; -25,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-21,36%</t>
+          <t>-4,48%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -3,16</t>
+          <t>-17,93; -3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 2,98</t>
+          <t>-10,54; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -9,41</t>
+          <t>-26,35; -9,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 2,34</t>
+          <t>-7,14; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,16; -15,25</t>
+          <t>-70,03; -21,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 21,02</t>
+          <t>-46,67; 27,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,85; -28,19</t>
+          <t>-63,69; -27,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 10,29</t>
+          <t>-26,21; 25,91</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-7,68%</t>
+          <t>-9,7%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 0,74</t>
+          <t>-11,07; 1,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -3,82</t>
+          <t>-18,78; -4,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,8; -7,56</t>
+          <t>-20,01; -6,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 3,99</t>
+          <t>-10,7; 3,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 7,04</t>
+          <t>-51,6; 13,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,91; -13,89</t>
+          <t>-55,86; -18,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,89; -33,98</t>
+          <t>-68,42; -31,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 11,16</t>
+          <t>-24,14; 9,45</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-9,93</t>
+          <t>-6,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-35,5%</t>
+          <t>-21,27%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -8,85</t>
+          <t>-17,02; -8,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -5,1</t>
+          <t>-14,33; -4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -1,29</t>
+          <t>-11,4; -1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -2,72</t>
+          <t>-10,85; -1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-65,43; -39,94</t>
+          <t>-66,11; -40,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,7; -20,37</t>
+          <t>-48,41; -18,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,45; -4,81</t>
+          <t>-34,43; -6,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,0; -9,86</t>
+          <t>-33,62; -6,46</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-7,4</t>
+          <t>-12,0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-59,35%</t>
+          <t>-70,47%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -5,22</t>
+          <t>-12,6; -5,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -8,49</t>
+          <t>-17,38; -8,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -10,05</t>
+          <t>-18,69; -9,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -0,29</t>
+          <t>-15,31; -8,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,62; -32,1</t>
+          <t>-60,93; -34,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,04; -30,92</t>
+          <t>-54,04; -30,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,98; -29,71</t>
+          <t>-47,88; -28,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,64; -9,83</t>
+          <t>-78,63; -59,42</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-7,14</t>
+          <t>-7,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-26,48%</t>
+          <t>-26,51%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -7,15</t>
+          <t>-10,64; -7,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -10,58</t>
+          <t>-14,51; -10,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -11,9</t>
+          <t>-15,71; -11,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -1,12</t>
+          <t>-9,73; -5,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-48,63; -35,34</t>
+          <t>-48,97; -34,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-50,98; -40,18</t>
+          <t>-50,67; -39,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -37,84</t>
+          <t>-47,31; -37,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-37,77; -7,67</t>
+          <t>-31,93; -20,2</t>
         </is>
       </c>
     </row>
